--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488203_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488203_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1265</v>
+        <v>9.615</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3226</v>
+        <v>8.008100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8039</v>
+        <v>1.6069</v>
       </c>
       <c r="G2" t="n">
         <v>5.495</v>
@@ -610,13 +610,13 @@
         <v>4.6322</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8687</v>
+        <v>-0.3802</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9302</v>
+        <v>-0.2446</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0614</v>
+        <v>-0.1356</v>
       </c>
       <c r="V2" t="n">
         <v>2.8327</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1883</v>
+        <v>2.4125</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1883</v>
+        <v>2.4196</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.0071</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1883</v>
+        <v>-0.7892</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3221</v>
+        <v>-1.2453</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8662</v>
+        <v>0.4562</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1883</v>
+        <v>1.273</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3221</v>
+        <v>0.4636</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8662</v>
+        <v>0.8093</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-2.0621</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.709</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.3531</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.1122</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.4278</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.8888</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8737</v>
+        <v>2.1883</v>
       </c>
       <c r="E4" t="n">
-        <v>1.93</v>
+        <v>2.1883</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0563</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7892</v>
+        <v>2.1883</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2453</v>
+        <v>0.3221</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4562</v>
+        <v>1.8662</v>
       </c>
       <c r="J4" t="n">
-        <v>1.273</v>
+        <v>2.1883</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4636</v>
+        <v>0.3221</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8093</v>
+        <v>1.8662</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0621</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.709</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3531</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0789</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6019</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.477</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8888</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9762999999999999</v>
+        <v>1.1234</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8809</v>
+        <v>1.9789</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.8554</v>
       </c>
       <c r="G5" t="n">
         <v>-0.08</v>
@@ -844,13 +844,13 @@
         <v>4.2616</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2407</v>
+        <v>-0.0936</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1679</v>
+        <v>-0.0699</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2851</v>
+        <v>-0.5262</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6369</v>
+        <v>0.0926</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.922</v>
+        <v>-0.6189</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0711</v>
+        <v>-0.5809</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.6623</v>
+        <v>-0.6639</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5913</v>
+        <v>0.0829</v>
       </c>
       <c r="J7" t="n">
-        <v>1.123</v>
+        <v>0.1474</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4126</v>
+        <v>0.0644</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5357</v>
+        <v>0.0829</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.1941</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.2497</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.891</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.4469</v>
+        <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9712</v>
+        <v>-0.3159</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5171</v>
+        <v>-0.0547</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.2611</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5262</v>
+        <v>-1.0383</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0926</v>
+        <v>-0.0066</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6189</v>
+        <v>-1.0317</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5809</v>
+        <v>-2.1817</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6639</v>
+        <v>-2.6979</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0829</v>
+        <v>0.5161</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1474</v>
+        <v>-0.5256</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0644</v>
+        <v>-1.2413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0829</v>
+        <v>0.7157</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-1.6561</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-1.4566</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.1996</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3159</v>
+        <v>-0.1536</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0547</v>
+        <v>0.2046</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2611</v>
+        <v>-0.3581</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8771</v>
+        <v>-1.3372</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8068</v>
+        <v>-0.5383</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9297</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.644</v>
+        <v>-3.0711</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.828</v>
+        <v>-3.6623</v>
       </c>
       <c r="I9" t="n">
-        <v>0.184</v>
+        <v>0.5913</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0011</v>
+        <v>1.123</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1798</v>
+        <v>-0.4126</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8212</v>
+        <v>1.5357</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6451</v>
+        <v>-4.1941</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0078</v>
+        <v>-3.2497</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6373</v>
+        <v>-0.9444</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.891</v>
       </c>
       <c r="R9" t="n">
-        <v>4.0763</v>
+        <v>4.4469</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8961</v>
+        <v>-0.0808</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0831</v>
+        <v>0.342</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.187</v>
+        <v>-0.4228</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6736</v>
+        <v>-1.4296</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1739</v>
+        <v>0.5656</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8475</v>
+        <v>-1.9952</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3309</v>
@@ -1234,13 +1234,13 @@
         <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0102</v>
+        <v>0.2338</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3283</v>
+        <v>0.0634</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3181</v>
+        <v>0.1704</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2589</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7244</v>
+        <v>-1.4887</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5942</v>
+        <v>-2.4923</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1302</v>
+        <v>1.0036</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1817</v>
+        <v>-1.644</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6979</v>
+        <v>-1.828</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5161</v>
+        <v>0.184</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5256</v>
+        <v>1.0011</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2413</v>
+        <v>0.1798</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7157</v>
+        <v>0.8212</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6561</v>
+        <v>-2.6451</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4566</v>
+        <v>-2.0078</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1996</v>
+        <v>-0.6373</v>
       </c>
       <c r="P11" t="n">
-        <v>1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.891</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>4.0763</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8396</v>
+        <v>0.2845</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.383</v>
+        <v>0.3976</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4566</v>
+        <v>-0.1132</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>-0.3144</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8872</v>
+        <v>-2.2538</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1196</v>
+        <v>-1.6093</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.6445</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7403</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2972</v>
+        <v>-0.0693</v>
       </c>
       <c r="T12" t="n">
-        <v>0.868</v>
+        <v>0.3784</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5708</v>
+        <v>-0.4477</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7736</v>
+        <v>-2.8481</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0716</v>
+        <v>-1.9737</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.702</v>
+        <v>-0.8743</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5272</v>
@@ -1468,13 +1468,13 @@
         <v>3.5205</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4745</v>
+        <v>0.4001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1131</v>
+        <v>-0.0152</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5877</v>
+        <v>0.4153</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2033</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.739699999999999</v>
+        <v>4.7394</v>
       </c>
       <c r="E14" t="n">
-        <v>8.955099999999998</v>
+        <v>8.955000000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.2156</v>
+        <v>-4.2155</v>
       </c>
       <c r="G14" t="n">
         <v>-6.939900000000002</v>
@@ -1546,19 +1546,19 @@
         <v>26.8667</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7149999999999999</v>
+        <v>-0.715</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8890999999999993</v>
+        <v>0.8894000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6041</v>
+        <v>-1.6042</v>
       </c>
       <c r="V14" t="n">
         <v>2.2038</v>
       </c>
       <c r="W14" t="n">
-        <v>9.754700000000001</v>
+        <v>9.7547</v>
       </c>
       <c r="X14" t="n">
         <v>-7.550800000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4773</v>
+        <v>2.5655</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4414</v>
+        <v>0.6962</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9641</v>
+        <v>1.8693</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1209</v>
+        <v>1.516</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4101</v>
+        <v>-0.358</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.531</v>
+        <v>1.874</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5758</v>
+        <v>1.6139</v>
       </c>
       <c r="K15" t="n">
-        <v>2.327</v>
+        <v>0.1932</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2488</v>
+        <v>1.4207</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6967</v>
+        <v>-0.098</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.5513</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.7798</v>
+        <v>0.4533</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>3.081</v>
+        <v>0.3084</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4983</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5827</v>
+        <v>0.2997</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.1466</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0014</v>
+        <v>1.3541</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3045</v>
+        <v>5.1248</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6969</v>
+        <v>-3.7707</v>
       </c>
       <c r="G16" t="n">
-        <v>1.516</v>
+        <v>5.1525</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.358</v>
+        <v>7.667</v>
       </c>
       <c r="I16" t="n">
-        <v>1.874</v>
+        <v>-2.5145</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6139</v>
+        <v>9.656000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1932</v>
+        <v>9.022</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4207</v>
+        <v>0.634</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.098</v>
+        <v>-4.5035</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5513</v>
+        <v>-1.355</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4533</v>
+        <v>-3.1485</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7411</v>
+        <v>-3.891</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>-5.5586</v>
       </c>
       <c r="R16" t="n">
         <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2557</v>
+        <v>0.0926</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.383</v>
+        <v>0.3986</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1273</v>
+        <v>-0.3059</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5992</v>
+        <v>1.3435</v>
       </c>
       <c r="E17" t="n">
-        <v>5.3207</v>
+        <v>3.9724</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.7215</v>
+        <v>-2.6289</v>
       </c>
       <c r="G17" t="n">
-        <v>5.1525</v>
+        <v>-1.1209</v>
       </c>
       <c r="H17" t="n">
-        <v>7.667</v>
+        <v>1.4101</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5145</v>
+        <v>-2.531</v>
       </c>
       <c r="J17" t="n">
-        <v>9.656000000000001</v>
+        <v>2.5758</v>
       </c>
       <c r="K17" t="n">
-        <v>9.022</v>
+        <v>2.327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.634</v>
+        <v>0.2488</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.5035</v>
+        <v>-3.6967</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.355</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.1485</v>
+        <v>-2.7798</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.891</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.5586</v>
+        <v>-2.7793</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3377</v>
+        <v>0.9473</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5944</v>
+        <v>1.0294</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2567</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6289</v>
+        <v>3.1466</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CALLE GÓMEZ</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6221</v>
+        <v>0.7599</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6221</v>
+        <v>-0.4524</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.2123</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6221</v>
+        <v>2.5053</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.2488</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6221</v>
+        <v>1.2565</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6221</v>
+        <v>1.5214</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.7642</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6221</v>
+        <v>0.7572</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.9839</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.4846</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.4993</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.116</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.1209</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>A. CALLE GÓMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5881</v>
+        <v>0.6221</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5503</v>
+        <v>0.6221</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1384</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5053</v>
+        <v>0.6221</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2488</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2565</v>
+        <v>0.6221</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5214</v>
+        <v>0.6221</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7642</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7572</v>
+        <v>0.6221</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9839</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4846</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4993</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2878</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2189</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0689</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CARBU RODRIGUEZ</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2991</v>
+        <v>-0.0614</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9944</v>
+        <v>-0.1158</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6953</v>
+        <v>0.0544</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4796</v>
+        <v>0.0281</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0464</v>
+        <v>0.9175</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4332</v>
+        <v>-0.8894</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0415</v>
+        <v>0.8567</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.1718</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>0.6849</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4381</v>
+        <v>-0.8285</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0464</v>
+        <v>0.7457</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3917</v>
+        <v>-1.5743</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1477</v>
+        <v>-0.6454</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1094</v>
+        <v>-0.046</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2572</v>
+        <v>-0.5994</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>J. CARBU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4778</v>
+        <v>-0.3237</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5075</v>
+        <v>-0.9944</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0297</v>
+        <v>0.6707</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0281</v>
+        <v>0.4796</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9175</v>
+        <v>0.0464</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8894</v>
+        <v>0.4332</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8567</v>
+        <v>0.0415</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1718</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6849</v>
+        <v>0.0415</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8285</v>
+        <v>0.4381</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7457</v>
+        <v>0.0464</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5743</v>
+        <v>0.3917</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0617</v>
+        <v>0.1231</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4377</v>
+        <v>-0.1094</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.624</v>
+        <v>0.2325</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6338</v>
+        <v>-1.3154</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3071</v>
+        <v>0.6009</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9408</v>
+        <v>-1.9162</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2736</v>
@@ -2248,13 +2248,13 @@
         <v>0.1853</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2659</v>
+        <v>0.0525</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1641</v>
+        <v>0.1296</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1017</v>
+        <v>-0.0771</v>
       </c>
       <c r="V23" t="n">
         <v>1.5733</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8344</v>
+        <v>-2.2602</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1852</v>
+        <v>-1.1549</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6492</v>
+        <v>-1.1052</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.959</v>
+        <v>-0.6529</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3186</v>
+        <v>0.0337</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6404</v>
+        <v>-0.6865</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5353</v>
+        <v>0.0654</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4938</v>
+        <v>0.6139</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0415</v>
+        <v>-0.5486</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4943</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8124</v>
+        <v>-0.5803</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6818</v>
+        <v>-0.138</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2455</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1641</v>
+        <v>-0.0143</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0813</v>
+        <v>0.092</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.63</v>
+        <v>-0.9439</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.63</v>
+        <v>1.5733</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.5172</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8693</v>
+        <v>-2.355</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6131</v>
+        <v>-1.1234</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2562</v>
+        <v>-1.2316</v>
       </c>
       <c r="G25" t="n">
         <v>2.9409</v>
@@ -2404,13 +2404,13 @@
         <v>2.7793</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1252</v>
+        <v>-0.6109</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6566</v>
+        <v>-0.1669</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4686</v>
+        <v>-0.444</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8321</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.0447</v>
+        <v>-2.5647</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7425</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3022</v>
+        <v>-1.5753</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6529</v>
+        <v>-1.959</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0337</v>
+        <v>-0.3186</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6865</v>
+        <v>-1.6404</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0654</v>
+        <v>0.5353</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6139</v>
+        <v>0.4938</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5486</v>
+        <v>0.0415</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-2.4943</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5803</v>
+        <v>-0.8124</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.138</v>
+        <v>-1.6818</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R26" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7068</v>
+        <v>0.0242</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6019</v>
+        <v>0.0317</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.105</v>
+        <v>-0.0075</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9439</v>
+        <v>-0.63</v>
       </c>
       <c r="W26" t="n">
-        <v>1.5733</v>
+        <v>-0.63</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.5172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.1348</v>
+        <v>-3.7705</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.4534</v>
+        <v>-3.2369</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6813</v>
+        <v>-0.5336</v>
       </c>
       <c r="G27" t="n">
         <v>-2.5642</v>
@@ -2560,13 +2560,13 @@
         <v>2.0382</v>
       </c>
       <c r="S27" t="n">
-        <v>1.0971</v>
+        <v>0.4614</v>
       </c>
       <c r="T27" t="n">
-        <v>1.2473</v>
+        <v>0.4639</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1502</v>
+        <v>-0.0025</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2596,13 +2596,13 @@
         <v>-4.739599999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>4.2156</v>
+        <v>4.215399999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.954999999999998</v>
+        <v>-8.954800000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>6.940099999999999</v>
+        <v>6.940100000000001</v>
       </c>
       <c r="H28" t="n">
         <v>12.7378</v>
@@ -2623,7 +2623,7 @@
         <v>-14.9869</v>
       </c>
       <c r="N28" t="n">
-        <v>-4.3521</v>
+        <v>-4.352099999999999</v>
       </c>
       <c r="O28" t="n">
         <v>-10.6348</v>
@@ -2638,13 +2638,13 @@
         <v>16.6759</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7148999999999995</v>
+        <v>0.7149000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>1.6043</v>
+        <v>1.6044</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.8892000000000001</v>
+        <v>-0.8892999999999999</v>
       </c>
       <c r="V28" t="n">
         <v>-2.2039</v>
